--- a/AAII_Financials/Quarterly/SIHBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SIHBY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>SIHBY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -667,63 +667,71 @@
     <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -760,8 +768,14 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +812,14 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,8 +856,14 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,8 +878,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -890,8 +918,14 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,8 +962,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -966,8 +1006,14 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,8 +1050,14 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,8 +1069,10 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1055,8 +1109,14 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1093,8 +1153,14 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,8 +1175,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1147,8 +1215,14 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1185,8 +1259,14 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1223,8 +1303,14 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1261,8 +1347,14 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1299,8 +1391,14 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,8 +1435,14 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1375,8 +1479,14 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1413,8 +1523,14 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1567,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1611,14 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1655,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,8 +1699,14 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1603,8 +1743,14 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1641,8 +1787,14 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,8 +1831,14 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1717,51 +1875,63 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1946,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,122 +1964,142 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>248200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>122500</v>
+      </c>
+      <c r="F41" s="3">
         <v>121200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>100500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>70200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>68200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>138000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>112700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>68700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>91200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>138000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>112700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>68700</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>184500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>126600</v>
+      </c>
+      <c r="F42" s="3">
         <v>64000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>51600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>65100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>77000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>28400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>54100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>66200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>55200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>28400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>54100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>66200</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F43" s="3">
         <v>20900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>39500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>33400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>20800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>36800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>76500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>9400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>36800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>76500</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1924,218 +2116,254 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>100</v>
+      </c>
+      <c r="P44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F45" s="3">
         <v>10400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>28000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>28000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>468500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>276400</v>
+      </c>
+      <c r="F46" s="3">
         <v>216500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>200100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>169000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>166500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>203900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>205400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>213600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>166900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>203900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>205400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>213600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>717300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>813900</v>
+      </c>
+      <c r="F47" s="3">
         <v>778200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>725500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>708900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>706500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>656100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>680400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>658200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>665100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>656100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>680400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>658200</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>40200</v>
+      </c>
+      <c r="F48" s="3">
         <v>39900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>37500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>38200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>43500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>41800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>45200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>46200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>40500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>41800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>45200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>46200</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>771200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>773500</v>
+      </c>
+      <c r="F49" s="3">
         <v>779600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>783000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>805400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>817600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>790900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>833600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>823100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>779200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>790900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>833600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>823100</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2400,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,28 +2444,34 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>100</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2248,8 +2488,14 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2532,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2116100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1907700</v>
+      </c>
+      <c r="F54" s="3">
         <v>1819300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1754000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1733000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1750600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1717200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1793200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1771700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1673200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1717200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1793200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1771700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2598,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,198 +2616,230 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>28100</v>
+      </c>
+      <c r="F57" s="3">
         <v>27700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>27900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>96800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>28200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>120500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>98300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>103800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>92000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>120500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>98300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>103800</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>569700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>502200</v>
+      </c>
+      <c r="F58" s="3">
         <v>426000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>426000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>264900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>257600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>227200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>226000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>167400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>226900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>227200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>226000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>167400</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>26800</v>
+      </c>
+      <c r="F59" s="3">
         <v>59300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>26300</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>34000</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>677100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>566000</v>
+      </c>
+      <c r="F60" s="3">
         <v>519500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>487000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>361700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>329000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>347700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>325700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>271900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>319000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>347700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>325700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>271900</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>191600</v>
+      </c>
+      <c r="F61" s="3">
         <v>187800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>195600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>302300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>312900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>325300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>344600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>409600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>313500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>325300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>344600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>409600</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2584,8 +2876,14 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2920,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2964,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,46 +3008,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>884900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>785300</v>
+      </c>
+      <c r="F66" s="3">
         <v>733500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>707400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>688000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>664200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>693200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>690800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>700900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>653100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>693200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>690800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>700900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +3074,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +3114,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +3158,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2866,8 +3202,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3246,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>288800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>273400</v>
+      </c>
+      <c r="F72" s="3">
         <v>234300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>197900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>201600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>222800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>192300</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>191800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>192300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>191800</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3334,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3378,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3422,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>753100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>664200</v>
+      </c>
+      <c r="F76" s="3">
         <v>646200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>623400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>631100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>670000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>624600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>684500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>657700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>618500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>624600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>684500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>657700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,51 +3510,63 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3213,8 +3603,14 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,46 +3625,54 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
+      <c r="E83" s="3">
+        <v>4400</v>
       </c>
       <c r="F83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3709,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3753,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3797,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3841,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,46 +3885,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F89" s="3">
         <v>21400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>18000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>29500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>10000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>28300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>19800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>13100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>28300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,46 +3951,54 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-24100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-18600</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-45900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-18600</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-45900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +4035,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,46 +4079,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-11700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>12300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-25800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>47100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>25500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-11300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>47100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>25500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +4145,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3688,37 +4156,43 @@
         <v>4</v>
       </c>
       <c r="E96" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>33100</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>24600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3">
         <v>24700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>14400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +4229,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4273,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,118 +4317,142 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-18400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-27400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-12900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-9800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-31100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-10100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-206900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-45500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-31100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-10100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-206900</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>15600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-25600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>31200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>43700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-198300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-45900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>31200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>43700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-198300</v>
       </c>
     </row>
